--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,7 +404,33 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Date/heure de l'attestation de validité </t>
+  </si>
+  <si>
+    <t>Authenticator.time.nullFlavor</t>
+  </si>
+  <si>
+    <t>Authenticator.time.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://hl7.org/cda/stds/core/StructureDefinition/ts-simple}
+</t>
+  </si>
+  <si>
+    <t>Date et heure à laquelle le PS atteste la validité des informations portées sur le document. Précisée à la seconde avec précision du décalage 
+par rapport au temps universel (UTC)</t>
+  </si>
+  <si>
+    <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
+  </si>
+  <si>
+    <t>TS.value</t>
+  </si>
+  <si>
     <t>Authenticator.signatureCode</t>
+  </si>
+  <si>
+    <t>Signature</t>
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/ValueSet/CDASignatureCode</t>
@@ -414,21 +440,153 @@
 </t>
   </si>
   <si>
-    <t>Authenticator.sdtcSignatureText</t>
+    <t>Authenticator.signatureCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.code</t>
+  </si>
+  <si>
+    <t>S pour 'signed'</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
   </si>
   <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Authenticator.signatureCode.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>Authenticator.sdtcSignatureText</t>
+  </si>
+  <si>
     <t>A textual or multimedia depiction of the signature by which the participant endorses his or her participation in the Act as specified in the Participation.typeCode and that he or she agrees to assume the associated accountability.</t>
   </si>
   <si>
     <t>Authenticator.assignedEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
+  </si>
+  <si>
+    <t>Entité attestant la validité</t>
   </si>
 </sst>
 </file>
@@ -730,11 +888,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.1484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.1484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.03515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -1005,7 +1163,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1308,7 +1466,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1409,7 +1567,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1512,7 +1670,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1920,7 +2078,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2031,7 +2189,9 @@
       <c r="K13" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2102,18 +2262,20 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>75</v>
@@ -2128,10 +2290,12 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="M14" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2161,7 +2325,7 @@
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2179,10 +2343,10 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>75</v>
@@ -2191,7 +2355,7 @@
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>74</v>
@@ -2199,10 +2363,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2225,9 +2389,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
         <v>132</v>
       </c>
@@ -2280,7 +2446,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2300,10 +2466,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2326,9 +2492,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L16" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2355,13 +2523,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2379,7 +2545,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2391,9 +2557,1340 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="185">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -404,7 +404,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Date/heure de l'attestation de validité </t>
+    <t>Date/heure de l'attestation de validité</t>
   </si>
   <si>
     <t>Authenticator.time.nullFlavor</t>
@@ -417,8 +417,7 @@
 </t>
   </si>
   <si>
-    <t>Date et heure à laquelle le PS atteste la validité des informations portées sur le document. Précisée à la seconde avec précision du décalage 
-par rapport au temps universel (UTC)</t>
+    <t>Date et heure à laquelle le PS atteste la validité des informations portées sur le document. Précisée à la seconde avec précision du décalage par rapport au temps universel (UTC)</t>
   </si>
   <si>
     <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
@@ -430,7 +429,7 @@
     <t>Authenticator.signatureCode</t>
   </si>
   <si>
-    <t>Signature</t>
+    <t>signatureCode signifie que le professionnel a validé les informations portées sur le document.</t>
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/ValueSet/CDASignatureCode</t>
@@ -444,9 +443,6 @@
   </si>
   <si>
     <t>Authenticator.signatureCode.code</t>
-  </si>
-  <si>
-    <t>S pour 'signed'</t>
   </si>
   <si>
     <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
@@ -2696,11 +2692,9 @@
       <c r="K18" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="L18" s="2"/>
+      <c r="M18" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2751,7 +2745,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2771,17 +2765,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2803,7 +2797,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2854,7 +2848,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2874,17 +2868,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2906,7 +2900,7 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2957,7 +2951,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2977,17 +2971,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -3009,7 +3003,7 @@
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3060,7 +3054,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3080,17 +3074,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -3112,7 +3106,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3163,7 +3157,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3183,10 +3177,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3209,11 +3203,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3264,7 +3258,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3284,10 +3278,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3314,7 +3308,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3365,7 +3359,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3385,39 +3379,39 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3468,7 +3462,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3488,39 +3482,39 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="F26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3571,7 +3565,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3591,39 +3585,39 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3674,7 +3668,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3694,10 +3688,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3720,11 +3714,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3775,7 +3769,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3795,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3821,10 +3815,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3876,7 +3870,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>Authenticator.typeId.nullFlavor</t>
@@ -1438,7 +1442,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1446,10 +1450,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1547,17 +1551,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1575,11 +1579,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1630,7 +1634,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1650,17 +1654,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1678,11 +1682,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1733,7 +1737,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1753,17 +1757,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1781,11 +1785,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1794,7 +1798,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1836,7 +1840,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1856,17 +1860,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1884,11 +1888,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1939,7 +1943,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1959,10 +1963,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1989,7 +1993,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2040,7 +2044,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2060,10 +2064,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2097,7 +2101,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2119,7 +2123,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2137,7 +2141,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2157,10 +2161,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2183,10 +2187,10 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2238,7 +2242,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2258,10 +2262,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2359,10 +2363,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2385,13 +2389,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2442,7 +2446,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2462,10 +2466,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2491,7 +2495,7 @@
         <v>91</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2523,7 +2527,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2541,7 +2545,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2553,7 +2557,7 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>74</v>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2662,10 +2666,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2694,7 +2698,7 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2745,7 +2749,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2765,17 +2769,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2793,11 +2797,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2848,7 +2852,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2868,17 +2872,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2896,11 +2900,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2951,7 +2955,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2971,17 +2975,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -2999,11 +3003,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3054,7 +3058,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3074,17 +3078,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -3102,11 +3106,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3157,7 +3161,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3177,10 +3181,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3203,11 +3207,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3258,7 +3262,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3278,10 +3282,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3304,11 +3308,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3359,7 +3363,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3379,17 +3383,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3407,11 +3411,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3462,7 +3466,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3482,17 +3486,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3510,11 +3514,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3565,7 +3569,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3585,17 +3589,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3613,11 +3617,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3668,7 +3672,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3688,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3714,11 +3718,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3769,7 +3773,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3789,10 +3793,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3815,10 +3819,10 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -3870,7 +3874,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Authenticator, professionnel (personne physique) attestant la validité du contenu du document.</t>
+    <t>L'élément de l'en-tête du CDA authenticator permet de représenter le professionnel (personne physique) attestant la validité du contenu du document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
